--- a/data/demo_data/wvs/questions.xlsx
+++ b/data/demo_data/wvs/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\demo_data\wvs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B63748-3741-4018-8469-0EC7F835AC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFDA80D-3E83-4BBD-9AF6-21BFDADC54BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32865" yWindow="1275" windowWidth="22605" windowHeight="19065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30000" yWindow="1650" windowWidth="35175" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -117,9 +117,6 @@
     <t>Q62</t>
   </si>
   <si>
-    <t>How much do you trust people of another religion? (on a scale 1 = trust completely; 2 = trust somewhat; 3 = do not trust very much; 4 = do not trust at all)</t>
-  </si>
-  <si>
     <t>Q63</t>
   </si>
   <si>
@@ -180,18 +177,6 @@
     <t>How important is God in your life? (on a scale of ' not at all important' to 'very important')</t>
   </si>
   <si>
-    <t>Here is a list of qualities that children can be encouraged to learn at home. Which, if any, do you consider to be especially important? Independence (on a scale of 'mentioned' to 'did not mention')</t>
-  </si>
-  <si>
-    <t>Here is a list of qualities that children can be encouraged to learn at home. Which, if any, do you consider to be especially important? Determination, perseverance (on a scale of 'mentioned' to 'did not mention')</t>
-  </si>
-  <si>
-    <t>Here is a list of qualities that children can be encouraged to learn at home. Which, if any, do you consider to be especially important? Religious faith (on a scale of 'mentioned' to 'did not mention')</t>
-  </si>
-  <si>
-    <t>Here is a list of qualities that children can be encouraged to learn at home. Which, if any, do you consider to be especially important? Obedience (on a scale of 'mentioned' to 'did not mention')</t>
-  </si>
-  <si>
     <t>In the future, would it be a good thing if we had greater respect for authority? (on a scale of 'good' to 'bad')</t>
   </si>
   <si>
@@ -201,9 +186,6 @@
     <t>How proud are you to be of the nationality of this country? (on a scale fo 'very proud' to  'I am not from this country')</t>
   </si>
   <si>
-    <t>Please tell me for each of the following actions whether you think it can always be justified, never be justified, or something in between: Abortion (on a scale of 'never justifiable' to 'always justifiable')</t>
-  </si>
-  <si>
     <t>How important is work to you? (on a scale of 'very important' to 'not at all important')</t>
   </si>
   <si>
@@ -219,30 +201,12 @@
     <t>Could you tell me how secure do you feel these days in your neighborhood? (on a scale of 'very secure' to 'not at all secure')</t>
   </si>
   <si>
-    <t>To what degree are you worried about the following situations? Losing my job or not finding a job (on a scaleof 'very much' to 'not at all')</t>
-  </si>
-  <si>
-    <t>Most people consider both freedom and security to be important, but if you had to choose between them, do you think security is more important than freedom (on a scale of 'freedom' to 'security')</t>
-  </si>
-  <si>
     <t>Do you feel happy? (on a scale of 'very happy' to 'not at all happy')</t>
   </si>
   <si>
     <t>How satisfied are you with your life? (on a scale of 'completely dissatisfied' to 'completely satisfied')</t>
   </si>
   <si>
-    <t>On this list are various groups of people. Could you please mention any that you would not like to have as neighbors? (on a scale of 'mentioned' to 'did not mention')</t>
-  </si>
-  <si>
-    <t>Please tell me for each of the following actions whether you think it can always be justified, never be justified, or something in between: Homosexuality (on a scale of 'never justifiable' to 'always justifiable')</t>
-  </si>
-  <si>
-    <t>I’m going to read out some forms of political action that people can take, and I'd like you to tell me, for each one, whether you have done any of these things, whether you might do it or would never under any circumstances do it: signing a petition (on a scale of 'have done' to 'would never do')</t>
-  </si>
-  <si>
-    <t>I’m going to read out some other forms of political action that people can take using Internet and social media tools like Facebook, Twitter etc., and I'd like you to tell me, for each one, whether you have done any of these things, whether you might do it or would never under any circumstances do it: signing an electronic petition (on a scale of 'have done' to 'would never do')</t>
-  </si>
-  <si>
     <t>Most people can be trusted (on a scale of 'most people can be trusted' to  'one needs to be very careful')</t>
   </si>
   <si>
@@ -273,21 +237,6 @@
     <t>Are you a member of a self-help or mutual aid group?  (on a scale of 'are an active member' to 'don't belong')</t>
   </si>
   <si>
-    <t>Please tell me for each of the following actions whether you think it can always be justified, never be justified, or something in between: Stealing property (on a scale of 'never justifiable' to 'always justifiable')</t>
-  </si>
-  <si>
-    <t>Please tell me for each of the following actions whether you think it can always be justified, never be justified, or something in between: Someone accepting a bribe in the course of their duties (on a scale of 'never justifiable' to 'always justifiable')</t>
-  </si>
-  <si>
-    <t>Please tell me for each of the following actions whether you think it can always be justified, never be justified, or something in between: Cheating on taxes if you have a chance (on a scale of 'never justifiable' to 'always justifiable')</t>
-  </si>
-  <si>
-    <t>Please tell me for each of the following actions whether you think it can always be justified, never be justified, or something in between: Violence against other people (on a scale of 'never justifiable' to 'always justifiable')</t>
-  </si>
-  <si>
-    <t>Please tell me for each of the following actions whether you think it can always be justified, never be justified, or something in between: For a man to beat his wife (on a scale of 'never justifiable' to 'always justifiable')</t>
-  </si>
-  <si>
     <t>How much confidence do you have in the parliament? (on a scale of ' a great deal' to 'none at all')</t>
   </si>
   <si>
@@ -303,16 +252,67 @@
     <t>How much confidence do you have in the justice system/courts? (on a scale of ' a great deal' to 'none at all')</t>
   </si>
   <si>
-    <t>To what degree are you worried about the following situations? A civil war (on a scale of 'very much' to ' not at all')</t>
-  </si>
-  <si>
-    <t>To what degree are you worried about the following situations? A terrorist attack (on a scale of 'very much' to ' not at all')</t>
-  </si>
-  <si>
-    <t>To what degree are you worried about the following situations? A war involving my country (on a scale of 'very much' to ' not at all')</t>
-  </si>
-  <si>
-    <t>To what degree are you worried about the following situations? Not being able to give one's children a good education (on a scale of 'very much' to ' not at all')</t>
+    <t>How much do you trust people of another religion? (on a scale of 'trust completely' to 'do not trust at all')</t>
+  </si>
+  <si>
+    <t>How especially important is the quality of independence for children to learn at home? (on a scale of 'mentioned' to 'did not mention')</t>
+  </si>
+  <si>
+    <t>How especially important are determination and perseverance for children to learn at home? (on a scale of 'mentioned' to 'did not mention')</t>
+  </si>
+  <si>
+    <t>How especially important is religious faith for children to learn at home? (on a scale of 'mentioned' to 'did not mention')</t>
+  </si>
+  <si>
+    <t>How especially important is the quality of obedience for children to learn at home? (on a scale of 'mentioned' to 'did not mention')</t>
+  </si>
+  <si>
+    <t>To what extent do you think abortion can be justified? (on a scale of 'never justifiable' to 'always justifiable')</t>
+  </si>
+  <si>
+    <t>How worried are you about losing your job or not being able to find a job? (on a scaleof 'very much' to 'not at all')</t>
+  </si>
+  <si>
+    <t>Could you please mention if you would not like to have homosexuals as neighbors? (on a scale of 'mentioned' to 'did not mention')</t>
+  </si>
+  <si>
+    <t>Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable')</t>
+  </si>
+  <si>
+    <t>Regarding 'signing an electronic petition' as a form of  political action that people can take using Internet and social media tools like Facebook, Twitter etc., and I'd like you to tell me, for each one, whether you have done any of these things, whether you might do it or would never under any circumstances do it. (on a scale of 'have done' to 'would never do')</t>
+  </si>
+  <si>
+    <t>Is 'stealing property' can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable')</t>
+  </si>
+  <si>
+    <t>Is 'someone accepting a bribe in the course of their duties' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable')</t>
+  </si>
+  <si>
+    <t>Is 'cheating on taxes if you have a chance' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable')</t>
+  </si>
+  <si>
+    <t>Is 'violence against other people' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable')</t>
+  </si>
+  <si>
+    <t>Is ' for a man to beat his wife ' can always be justified, never be justified, or something in between:(on a scale of 'never justifiable' to 'always justifiable')</t>
+  </si>
+  <si>
+    <t>To what degree are you worried about a civil war? (on a scale of 'very much' to ' not at all')</t>
+  </si>
+  <si>
+    <t>To what degree are you worried about a terrorist attack? (on a scale of 'very much' to ' not at all')</t>
+  </si>
+  <si>
+    <t>To what degree are you worried about a war involving my country? (on a scale of 'very much' to ' not at all')</t>
+  </si>
+  <si>
+    <t>To what degree are you worried about not being able to give one's children a good education? (on a scale of 'very much' to ' not at all')</t>
+  </si>
+  <si>
+    <t>Regarding 'signing a petition,' please you to tell me, whether you have done any of these things, whether you might do it or would never under any circumstances do it. (on a scale of 'have done' to 'would never do')</t>
+  </si>
+  <si>
+    <t>Most people consider both freedom and security to be important, but if you had to choose between them, do you think security is more important than freedom? (on a scale of 'freedom' to 'security')</t>
   </si>
 </sst>
 </file>
@@ -700,47 +700,47 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -748,7 +748,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -756,7 +756,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -764,7 +764,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -772,7 +772,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -780,7 +780,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -788,7 +788,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -796,7 +796,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -804,7 +804,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -812,7 +812,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.35">
@@ -820,7 +820,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
@@ -828,7 +828,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
@@ -836,15 +836,15 @@
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="29" x14ac:dyDescent="0.35">
@@ -852,15 +852,15 @@
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
@@ -868,7 +868,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
@@ -876,7 +876,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
@@ -884,7 +884,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
@@ -892,7 +892,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
@@ -900,7 +900,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
@@ -908,7 +908,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
@@ -916,159 +916,159 @@
         <v>29</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>48</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>49</v>
-      </c>
       <c r="B48" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
